--- a/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_04_Tier04_ElecOnly_85_Upfront100k_WPS.xlsx
+++ b/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_04_Tier04_ElecOnly_85_Upfront100k_WPS.xlsx
@@ -4659,13 +4659,13 @@
         <s:v>849.2885573270861</s:v>
       </s:c>
       <s:c r="D53" s="186" t="n">
-        <s:v>55.29402645721373</s:v>
+        <s:v>65.14442951632907</s:v>
       </s:c>
       <s:c r="E53" s="186" t="n">
-        <s:v>322548.4876670801</s:v>
+        <s:v>380009.1721785863</s:v>
       </s:c>
       <s:c r="F53" s="186" t="n">
-        <s:v>138235.0661430343</s:v>
+        <s:v>162861.0737908227</s:v>
       </s:c>
       <s:c r="G53" s="185" t="inlineStr">
         <s:is>
